--- a/foragingModelTable.xlsx
+++ b/foragingModelTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEBB6B9A-9E12-CC4B-B6F2-AEABA52BCFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC8FCA9-1451-0448-8C14-B578FDCB5930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11160" yWindow="3980" windowWidth="27240" windowHeight="16440" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
+    <workbookView xWindow="460" yWindow="500" windowWidth="27240" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/foragingModelTable.xlsx
+++ b/foragingModelTable.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/exs165/Dropbox/foraging/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC8FCA9-1451-0448-8C14-B578FDCB5930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434D1C92-4E2F-5241-8F27-B17FA0246812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="460" yWindow="500" windowWidth="27240" windowHeight="16320" xr2:uid="{AF09A64C-08B3-A642-B0D0-C38CF1EBFD20}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="21">
   <si>
     <t>softmax</t>
   </si>
@@ -50,12 +50,6 @@
     <t>fit</t>
   </si>
   <si>
-    <t>linear</t>
-  </si>
-  <si>
-    <t>twoLinear</t>
-  </si>
-  <si>
     <t>twoExponential</t>
   </si>
   <si>
@@ -93,6 +87,18 @@
   </si>
   <si>
     <t>learnRho</t>
+  </si>
+  <si>
+    <t>hyperbolic</t>
+  </si>
+  <si>
+    <t>twoHyperbolic</t>
+  </si>
+  <si>
+    <t>scalar</t>
+  </si>
+  <si>
+    <t>twoScalar</t>
   </si>
 </sst>
 </file>
@@ -452,27 +458,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F6688-A436-6A43-9B8F-A83A43AD55B0}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -492,7 +498,7 @@
         <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -500,7 +506,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -509,10 +515,10 @@
         <v>0</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -532,7 +538,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -552,7 +558,7 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -572,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -592,7 +598,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -612,7 +618,7 @@
         <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -629,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -649,10 +655,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -669,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="E11" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -689,10 +695,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -709,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
         <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -729,10 +735,10 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -749,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -769,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -789,10 +795,10 @@
         <v>0</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -809,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" t="s">
         <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -829,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -849,10 +855,130 @@
         <v>0</v>
       </c>
       <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" t="s">
         <v>6</v>
       </c>
-      <c r="F20" t="s">
-        <v>10</v>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
